--- a/data/generateProbability.xlsx
+++ b/data/generateProbability.xlsx
@@ -37,7 +37,7 @@
     <t>waveNumber</t>
   </si>
   <si>
-    <t>goblinId</t>
+    <t>enemyId</t>
   </si>
   <si>
     <t>name</t>
@@ -55,7 +55,7 @@
     <t>波数</t>
   </si>
   <si>
-    <t>哥布林编号</t>
+    <t>敌人编号</t>
   </si>
   <si>
     <t>名字</t>
@@ -1134,8 +1134,8 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="22.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="22.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="30.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">

--- a/data/generateProbability.xlsx
+++ b/data/generateProbability.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="generateProbability" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>waveNumber</t>
   </si>
@@ -70,16 +70,25 @@
     <t>哥布林</t>
   </si>
   <si>
+    <t>大哥布林</t>
+  </si>
+  <si>
     <t>哥布林斥候</t>
   </si>
   <si>
+    <t>哥布林弓箭手</t>
+  </si>
+  <si>
     <t>哥布林战士</t>
   </si>
   <si>
+    <t>哥布林骑士</t>
+  </si>
+  <si>
+    <t>哥布林法师</t>
+  </si>
+  <si>
     <t>野蛮哥布林</t>
-  </si>
-  <si>
-    <t>哥布林祭祀</t>
   </si>
 </sst>
 </file>
@@ -667,8 +676,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1129,13 +1141,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="30.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="23.225" customWidth="1"/>
+    <col min="3" max="3" width="31.225" customWidth="1"/>
+    <col min="4" max="4" width="30.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1180,339 +1192,521 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+    <row r="5" s="1" customFormat="1" spans="1:4">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
+      <c r="D5" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:4">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+    <row r="7" s="1" customFormat="1" spans="1:4">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="B7">
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:4">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:4">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
+      <c r="D9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:4">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:4">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:4">
+      <c r="A12" s="1">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:4">
+      <c r="A13" s="1">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="14" s="1" customFormat="1" spans="1:4">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:4">
+      <c r="A15" s="1">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:4">
+      <c r="A16" s="1">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:4">
+      <c r="A17" s="1">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:4">
+      <c r="A18" s="1">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:4">
+      <c r="A19" s="1">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:4">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
         <v>10</v>
       </c>
-      <c r="D8">
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:4">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="22" s="1" customFormat="1" spans="1:4">
+      <c r="A22" s="1">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:4">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:4">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:4">
+      <c r="A25" s="1">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:4">
+      <c r="A26" s="1">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:4">
+      <c r="A27" s="1">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:4">
+      <c r="A28" s="1">
+        <v>8</v>
+      </c>
+      <c r="B28" s="1">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:4">
+      <c r="A29" s="1">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:4">
+      <c r="A30" s="1">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1">
+        <v>7</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:4">
+      <c r="A31" s="1">
+        <v>9</v>
+      </c>
+      <c r="B31" s="1">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:4">
+      <c r="A32" s="1">
+        <v>9</v>
+      </c>
+      <c r="B32" s="1">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:4">
+      <c r="A33" s="1">
+        <v>9</v>
+      </c>
+      <c r="B33" s="1">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:4">
+      <c r="A34" s="1">
+        <v>9</v>
+      </c>
+      <c r="B34" s="1">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:4">
+      <c r="A35" s="1">
+        <v>10</v>
+      </c>
+      <c r="B35" s="1">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:4">
+      <c r="A36" s="1">
+        <v>10</v>
+      </c>
+      <c r="B36" s="1">
+        <v>7</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:4">
+      <c r="A37" s="1">
+        <v>10</v>
+      </c>
+      <c r="B37" s="1">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:4">
+      <c r="A38" s="1">
         <v>11</v>
       </c>
-      <c r="D9">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
+      <c r="B38" s="1">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="39" s="1" customFormat="1" spans="1:4">
+      <c r="A39" s="1">
         <v>11</v>
       </c>
-      <c r="D12">
+      <c r="B39" s="1">
+        <v>7</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="40" s="1" customFormat="1" spans="1:4">
+      <c r="A40" s="1">
         <v>11</v>
       </c>
-      <c r="D15">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16">
+      <c r="B40" s="1">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>4</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>5</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="41" s="1" customFormat="1" spans="1:4">
+      <c r="A41" s="1">
         <v>11</v>
       </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>5</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>5</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
-        <v>5</v>
-      </c>
-      <c r="B21">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>6</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>6</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>6</v>
-      </c>
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>7</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>7</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27">
-        <v>7</v>
-      </c>
-      <c r="B27">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28">
-        <v>7</v>
-      </c>
-      <c r="B28">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28">
+      <c r="B41" s="1">
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="1">
         <v>20</v>
       </c>
     </row>

--- a/data/generateProbability.xlsx
+++ b/data/generateProbability.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="generateProbability" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>waveNumber</t>
   </si>
@@ -76,7 +76,7 @@
     <t>哥布林斥候</t>
   </si>
   <si>
-    <t>哥布林弓箭手</t>
+    <t>野蛮哥布林</t>
   </si>
   <si>
     <t>哥布林战士</t>
@@ -85,10 +85,13 @@
     <t>哥布林骑士</t>
   </si>
   <si>
-    <t>哥布林法师</t>
-  </si>
-  <si>
-    <t>野蛮哥布林</t>
+    <t>哥布林祭祀</t>
+  </si>
+  <si>
+    <t>精英哥布林</t>
+  </si>
+  <si>
+    <t>哥布林王</t>
   </si>
 </sst>
 </file>
@@ -1141,13 +1144,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="23.225" customWidth="1"/>
-    <col min="3" max="3" width="31.225" customWidth="1"/>
-    <col min="4" max="4" width="30.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="23.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="30.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1203,7 +1206,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
@@ -1217,7 +1220,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
@@ -1231,7 +1234,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
@@ -1245,21 +1248,21 @@
         <v>11</v>
       </c>
       <c r="D8" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
       <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
@@ -1267,18 +1270,18 @@
         <v>3</v>
       </c>
       <c r="B10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:4">
       <c r="A11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -1287,12 +1290,12 @@
         <v>12</v>
       </c>
       <c r="D11" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
       <c r="A12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -1306,55 +1309,55 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
       <c r="A13" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
       <c r="A15" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
       <c r="A16" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
       </c>
       <c r="D16" s="1">
         <v>20</v>
@@ -1362,111 +1365,111 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
       <c r="A17" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
       </c>
       <c r="D17" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:4">
       <c r="A18" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
       </c>
       <c r="D18" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
       <c r="A19" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1">
-        <v>5</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
       </c>
       <c r="D19" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
       <c r="A21" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D21" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
       <c r="A22" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
       <c r="A24" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D24" s="1">
         <v>20</v>
@@ -1474,242 +1477,19 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
       <c r="A25" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B25" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:4">
-      <c r="A26" s="1">
-        <v>7</v>
-      </c>
-      <c r="B26" s="1">
-        <v>6</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:4">
-      <c r="A27" s="1">
-        <v>7</v>
-      </c>
-      <c r="B27" s="1">
-        <v>7</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:4">
-      <c r="A28" s="1">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:4">
-      <c r="A29" s="1">
-        <v>8</v>
-      </c>
-      <c r="B29" s="1">
-        <v>6</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:4">
-      <c r="A30" s="1">
-        <v>8</v>
-      </c>
-      <c r="B30" s="1">
-        <v>7</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:4">
-      <c r="A31" s="1">
-        <v>9</v>
-      </c>
-      <c r="B31" s="1">
-        <v>5</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:4">
-      <c r="A32" s="1">
-        <v>9</v>
-      </c>
-      <c r="B32" s="1">
-        <v>6</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:4">
-      <c r="A33" s="1">
-        <v>9</v>
-      </c>
-      <c r="B33" s="1">
-        <v>7</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:4">
-      <c r="A34" s="1">
-        <v>9</v>
-      </c>
-      <c r="B34" s="1">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:4">
-      <c r="A35" s="1">
-        <v>10</v>
-      </c>
-      <c r="B35" s="1">
-        <v>6</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:4">
-      <c r="A36" s="1">
-        <v>10</v>
-      </c>
-      <c r="B36" s="1">
-        <v>7</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:4">
-      <c r="A37" s="1">
-        <v>10</v>
-      </c>
-      <c r="B37" s="1">
-        <v>8</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:4">
-      <c r="A38" s="1">
-        <v>11</v>
-      </c>
-      <c r="B38" s="1">
-        <v>6</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:4">
-      <c r="A39" s="1">
-        <v>11</v>
-      </c>
-      <c r="B39" s="1">
-        <v>7</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:4">
-      <c r="A40" s="1">
-        <v>11</v>
-      </c>
-      <c r="B40" s="1">
-        <v>8</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:4">
-      <c r="A41" s="1">
-        <v>11</v>
-      </c>
-      <c r="B41" s="1">
-        <v>9</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="1">
-        <v>20</v>
-      </c>
-    </row>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
